--- a/Result/profitability/5530.xlsx
+++ b/Result/profitability/5530.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.1</v>
       </c>
       <c r="M2" t="n">
-        <v>0.69875</v>
+        <v>0.73125</v>
       </c>
       <c r="N2" t="n">
-        <v>54.43</v>
+        <v>55.615</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.04</v>
       </c>
       <c r="M3" t="n">
-        <v>0.645</v>
+        <v>0.5449999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>43.40125</v>
+        <v>42.90875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.14</v>
       </c>
       <c r="M4" t="n">
-        <v>0.43625</v>
+        <v>0.4125</v>
       </c>
       <c r="N4" t="n">
-        <v>63.345</v>
+        <v>63.655</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.28</v>
       </c>
       <c r="M5" t="n">
-        <v>0.28625</v>
+        <v>0.3575</v>
       </c>
       <c r="N5" t="n">
-        <v>30.1225</v>
+        <v>29.67</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.08</v>
       </c>
       <c r="M6" t="n">
-        <v>0.25625</v>
+        <v>0.23875</v>
       </c>
       <c r="N6" t="n">
-        <v>20.29375</v>
+        <v>20.80125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0.14875</v>
+        <v>0.14125</v>
       </c>
       <c r="N7" t="n">
-        <v>13.94125</v>
+        <v>14.13</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05124999999999999</v>
+        <v>0.02374999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>7.716249999999999</v>
+        <v>7.453750000000001</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>-0.008750000000000008</v>
       </c>
       <c r="N9" t="n">
-        <v>3.554999999999999</v>
+        <v>3.555000000000001</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>0.08999999999999998</v>
       </c>
       <c r="N10" t="n">
-        <v>5.289999999999999</v>
+        <v>5.290000000000001</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>0.26</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.695000000000002</v>
+        <v>-1.694999999999999</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5530</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>985</v>
+      </c>
+      <c r="D75" t="n">
+        <v>395</v>
+      </c>
+      <c r="E75" t="n">
+        <v>590</v>
+      </c>
+      <c r="F75" t="n">
+        <v>59.92</v>
+      </c>
+      <c r="G75" t="n">
+        <v>221</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>22.42%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>108</v>
+      </c>
+      <c r="J75" t="n">
+        <v>329</v>
+      </c>
+      <c r="K75" t="n">
+        <v>308</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.8025</v>
+      </c>
+      <c r="N75" t="n">
+        <v>58.93625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.231578947368421</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.100000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03386004514672691</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>3.5625</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.619999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.0569719861504564</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
